--- a/tools/importer/reports/import-northern-california.report.xlsx
+++ b/tools/importer/reports/import-northern-california.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-07T21:18:53.941Z</t>
+    <t>2026-10-08T02:41:02.547Z</t>
   </si>
   <si>
     <t>Health and wellness | Kaiser Permanente</t>
@@ -70,7 +70,7 @@
     <t>northern-california</t>
   </si>
   <si>
-    <t>2026-10-07T21:32:44.900Z</t>
+    <t>2026-10-08T02:41:13.802Z</t>
   </si>
   <si>
     <t>Custom Care &amp; Coverage Just For You | Kaiser Permanente</t>
